--- a/사전사후_입력시트_H-IFIT.xlsx
+++ b/사전사후_입력시트_H-IFIT.xlsx
@@ -852,16 +852,16 @@
         </is>
       </c>
       <c r="C4" s="7" t="n">
-        <v>48.3</v>
+        <v>45</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>52.4</v>
+        <v>47.5</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G4" s="8" t="n">
         <v>2</v>
@@ -900,10 +900,10 @@
         <v>2</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U4" s="9">
         <f>IF(COUNT(G4,I4,K4,M4,O4,Q4,S4)=7,SUM(G4,I4,K4,M4,O4,Q4,S4),"")</f>
